--- a/InputData/land/AOCoLUPpUA/Annual Ongoing Cost of Land Use Pol per Unit Area.xlsx
+++ b/InputData/land/AOCoLUPpUA/Annual Ongoing Cost of Land Use Pol per Unit Area.xlsx
@@ -1,29 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27615"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\land\AOCoLUPpUA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-india\InputData\land\AOCoLUPpUA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF94B7C1-28EB-4AAB-A6C5-9A13131631C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_1E3AC258EC45BF9CC2D64E2D68951652D8407AC0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="AOCoLUPpUA" sheetId="3" r:id="rId2"/>
+    <sheet name="Forest Mgmt Costs - Kerala" sheetId="5" r:id="rId2"/>
+    <sheet name="Costs from ICoLUPpUA" sheetId="7" r:id="rId3"/>
+    <sheet name="AOCoLUPpUA" sheetId="3" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="C_to_CO2">'[1]Conversion Factors'!$A$4</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -32,6 +37,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,26 +45,274 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
   <si>
     <t>AOCoLUPpUA Annual Ongoing Cost of Land Use Policies per Unit Area</t>
   </si>
   <si>
-    <t>Source:</t>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Costs for general forest management in Kerala state (reference only)</t>
+  </si>
+  <si>
+    <t>NATIONAL MISSION FOR GREEN INDIA</t>
+  </si>
+  <si>
+    <t>Kerala Forests &amp; Wildlife Department</t>
+  </si>
+  <si>
+    <t>Ministry of Environment and Forests</t>
+  </si>
+  <si>
+    <t>Administration Report 2017-18</t>
+  </si>
+  <si>
+    <t>Tentative Mission Costs</t>
+  </si>
+  <si>
+    <t>http://www.forest.kerala.gov.in/images/abc/AdmnReport2017-18.pdf</t>
+  </si>
+  <si>
+    <t>https://web.archive.org/web/20190303154131/http://www.moef.gov.in/sites/default/files/GIM_Mission%20Document-1.pdf</t>
+  </si>
+  <si>
+    <t>Table 5.5, 5.6 (page 89); Table 1.6.6 (page 20)</t>
+  </si>
+  <si>
+    <t>ANNEX 1</t>
+  </si>
+  <si>
+    <t>Implementation Cost per Policy</t>
+  </si>
+  <si>
+    <r>
+      <t>See</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> land/ICoLUPpUA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> variable</t>
+    </r>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>This variable is for the costs to maintain lands previously affected by one of the</t>
+  </si>
+  <si>
+    <t>land use policies (such as "Avoid Deforestation" or "Peatland Restoration") and</t>
+  </si>
+  <si>
+    <t>avoid emission of sequestered CO2.</t>
+  </si>
+  <si>
+    <t>This variable is NOT for use with the Improved Forest Management policy,</t>
+  </si>
+  <si>
+    <t>as that policy must be repeated every year in order to obtain carbon benefits</t>
+  </si>
+  <si>
+    <t>in that year.  Its cost is handled in the "Implementation Cost of Land Use</t>
+  </si>
+  <si>
+    <t>Policies per Unit Area" variable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The general forest management expenditures are analysed from a representative </t>
+  </si>
+  <si>
+    <t xml:space="preserve">state in India. These include general maintenance expenditures directly related </t>
+  </si>
+  <si>
+    <t>to the land, under both central and state schemes. They don't include administrative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">costs or costs for any specific forest enhancement activities like restoration or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">conservation. Such state-level breakdowns of expenditures don't have labour costs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">which is a crucial component of maintenance activities in Indian forests. Hence, </t>
+  </si>
+  <si>
+    <t>we find these estimates to be too low.</t>
+  </si>
+  <si>
+    <t>Instead, we refer to the tentative costs of the National Mission for a Green India</t>
+  </si>
+  <si>
+    <t>(from ICoLUPpUA -Implementation Cost of Land Use Policies per Unit Area)</t>
+  </si>
+  <si>
+    <t>variable. The Mission document specifies a % of O&amp;M costs which is applied</t>
+  </si>
+  <si>
+    <t>to each policy. The Kerala state expenditures are retained for reference only.</t>
+  </si>
+  <si>
+    <t>Table 5.5-Achievements on PlanSchemes (Financial) during 2017-18</t>
+  </si>
+  <si>
+    <t>Rupees per dollar</t>
+  </si>
+  <si>
+    <t>Expenditure</t>
+  </si>
+  <si>
+    <t>See "scaling-factors.xlsx" for source info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. State Sector Schemes </t>
+  </si>
+  <si>
+    <t>(2018 lakh INR)</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Management of Natural Forests</t>
+  </si>
+  <si>
+    <t>USD 2018 to 2012 conversion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forest Protection </t>
+  </si>
+  <si>
+    <t>Multiply by to get 2012 Dollars</t>
+  </si>
+  <si>
+    <t>Forest Protection (Survey of Forest Boundaries &amp; ForestProtection)</t>
+  </si>
+  <si>
+    <t>See "cpi.xlsx" for source info</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>Human Resource Development</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>VIII</t>
+  </si>
+  <si>
+    <t>Forest Management IS&amp;GIS</t>
+  </si>
+  <si>
+    <t>XI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measures to reduce Man Animal Conflict </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Schemes with Central Assistance </t>
+  </si>
+  <si>
+    <t>viii</t>
+  </si>
+  <si>
+    <t>Integrated Forest Protection Scheme</t>
+  </si>
+  <si>
+    <t>Table 5.6-Achievements on Non-planSchemes (Financial) during 2017-18.</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forest Conservation Development &amp; Regeneration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Protection Work </t>
+  </si>
+  <si>
+    <t>Silvicultural Works</t>
+  </si>
+  <si>
+    <t>Forest Protection</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>2018 INR</t>
+  </si>
+  <si>
+    <t>2018 USD</t>
+  </si>
+  <si>
+    <t>2012 USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1.6.6 Distribution of forest area according to utilization as on 31.03.2018.    </t>
+  </si>
+  <si>
+    <t>Dense/Degraded Forest</t>
+  </si>
+  <si>
+    <t>km2</t>
+  </si>
+  <si>
+    <t>acres/km2</t>
+  </si>
+  <si>
+    <t>acres</t>
+  </si>
+  <si>
+    <t>Cost per acre</t>
+  </si>
+  <si>
+    <t>2012 USD/acre</t>
+  </si>
+  <si>
+    <t>policy implementation cost ($ / acre)</t>
+  </si>
+  <si>
+    <t>O&amp;M costs for Green India Mission</t>
+  </si>
+  <si>
     <t>forest set asides</t>
   </si>
   <si>
+    <t>O&amp;M %</t>
+  </si>
+  <si>
     <t>afforestation and reforestation</t>
   </si>
   <si>
+    <t>(assumed to be half of mission org, O&amp;M,</t>
+  </si>
+  <si>
     <t>improved forest management</t>
   </si>
   <si>
+    <t>contingencies and overheads component)</t>
+  </si>
+  <si>
     <t>avoid deforestation</t>
   </si>
   <si>
@@ -68,29 +322,17 @@
     <t>forest restoration</t>
   </si>
   <si>
+    <t>Source: MoEFCC, Annex I - Tentative Mission Costs</t>
+  </si>
+  <si>
     <t>annual maintenance cost ($ / acre)</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Based on consultation with the organization American Forests, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">annual ongoing for land affected by these policy levers is a </t>
-  </si>
-  <si>
-    <t>small part of lifetime costs. For this reason, we do not attempt</t>
-  </si>
-  <si>
-    <t>to track these in the US model.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,16 +371,71 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -182,8 +479,146 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
@@ -201,19 +636,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="8">
     <cellStyle name="Body: normal cell" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Footnotes: top row" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Header: bottom row" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Table title" xfId="6" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
@@ -231,8 +715,57 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>89438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>52495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AE9D9C7-43D9-40F9-9E4F-FC4DCD1E6D90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5010150" y="279938"/>
+          <a:ext cx="4200525" cy="2439557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="About"/>
@@ -276,22 +809,16 @@
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
-      <sheetData sheetId="19">
-        <row r="4">
-          <cell r="A4">
-            <v>3.6666666666666665</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="19"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -329,9 +856,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,26 +891,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -416,26 +926,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -609,129 +1102,844 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="11" max="11" width="51.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="K3" s="35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" s="2">
+        <v>2018</v>
+      </c>
+      <c r="K5" s="36">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="K8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="K10" s="35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="K11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1"/>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="4" max="4" width="43.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22"/>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2">
+        <v>2018</v>
+      </c>
+      <c r="H2" s="6">
+        <v>68.657300000000006</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="29"/>
+      <c r="G4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="12"/>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="30">
+        <v>2492.375</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="12"/>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="30">
+        <v>2612.529</v>
+      </c>
+      <c r="G6">
+        <v>2018</v>
+      </c>
+      <c r="H6">
+        <v>0.9143273584567535</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="30">
+        <v>5.9981900000000001</v>
+      </c>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="12"/>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="30">
+        <v>273</v>
+      </c>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="30">
+        <v>113.404</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="31">
+        <v>1313.8430000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="30"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="30">
+        <v>326.41899999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="15"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="30"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="32"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="33"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="12"/>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="30">
+        <v>18.34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="12"/>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="30">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="31">
+        <v>4597.5290000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="D19" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="33">
+        <f>SUM(E5:E18)*10^5</f>
+        <v>1176123719.0000002</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="D20" s="12"/>
+      <c r="E20" s="30">
+        <f>E19/H2</f>
+        <v>17130352.038312025</v>
+      </c>
+      <c r="F20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="D21" s="13"/>
+      <c r="E21" s="34">
+        <f>E20*H6</f>
+        <v>15662749.528624097</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="25">
+        <v>9023.9549999999999</v>
+      </c>
+      <c r="D24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="C25">
+        <v>247.10499999999999</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="C26">
+        <f>C24*C25</f>
+        <v>2229864.4002749999</v>
+      </c>
+      <c r="D26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="D28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="26">
+        <f>E21/C26</f>
+        <v>7.0240816108335897</v>
+      </c>
+      <c r="F28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A24:B24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="38">
+        <f>0.04/2</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="6">
+        <v>1042.7688329302873</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="6">
+        <v>5.9981900000000001</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:1" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:1" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:1" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+        <v>81</v>
+      </c>
+      <c r="B5">
+        <v>1443.1257987949609</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7">
+        <v>2781.0236747611216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="G16" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="B1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="6">
+        <f>'Costs from ICoLUPpUA'!B2*'Costs from ICoLUPpUA'!$D$2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="6">
+        <f>'Costs from ICoLUPpUA'!B3*'Costs from ICoLUPpUA'!$D$2</f>
+        <v>20.855376658605746</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="6">
+        <f>'Costs from ICoLUPpUA'!B4*'Costs from ICoLUPpUA'!$D$2</f>
+        <v>0.11996380000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="6">
+        <f>'Costs from ICoLUPpUA'!B5*'Costs from ICoLUPpUA'!$D$2</f>
+        <v>28.862515975899218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="6">
+        <f>'Costs from ICoLUPpUA'!B6*'Costs from ICoLUPpUA'!$D$2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="6">
+        <f>'Costs from ICoLUPpUA'!B7*'Costs from ICoLUPpUA'!$D$2</f>
+        <v>55.620473495222434</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7628774-C808-4F13-8ECD-7874535D00D9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E2E87DB-3811-4191-8413-FC120F619E9F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{045E852F-E64E-4303-AE87-53DD98E190D3}"/>
 </file>